--- a/artfynd/A 16252-2024 artfynd.xlsx
+++ b/artfynd/A 16252-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119839393</v>
       </c>
       <c r="B2" t="n">
-        <v>102825</v>
+        <v>102848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 16252-2024 artfynd.xlsx
+++ b/artfynd/A 16252-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,458 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121478101</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57462</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>520030</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6967798</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121479593</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>520021</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6967787</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121483107</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90709</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>520123</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6967781</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121479450</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90709</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>520036</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6967788</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16252-2024 artfynd.xlsx
+++ b/artfynd/A 16252-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121478101</v>
+        <v>121479450</v>
       </c>
       <c r="B3" t="n">
-        <v>57462</v>
+        <v>90710</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520030</v>
+        <v>520036</v>
       </c>
       <c r="R3" t="n">
-        <v>6967798</v>
+        <v>6967788</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -856,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121479593</v>
+        <v>121483107</v>
       </c>
       <c r="B4" t="n">
-        <v>79685</v>
+        <v>90710</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520021</v>
+        <v>520123</v>
       </c>
       <c r="R4" t="n">
-        <v>6967787</v>
+        <v>6967781</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121483107</v>
+        <v>121478101</v>
       </c>
       <c r="B5" t="n">
-        <v>90709</v>
+        <v>57462</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,41 +1013,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520123</v>
+        <v>520030</v>
       </c>
       <c r="R5" t="n">
-        <v>6967781</v>
+        <v>6967798</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121479450</v>
+        <v>121479593</v>
       </c>
       <c r="B6" t="n">
-        <v>90709</v>
+        <v>79685</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,21 +1133,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520036</v>
+        <v>520021</v>
       </c>
       <c r="R6" t="n">
-        <v>6967788</v>
+        <v>6967787</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 16252-2024 artfynd.xlsx
+++ b/artfynd/A 16252-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121479450</v>
+        <v>121478101</v>
       </c>
       <c r="B3" t="n">
-        <v>90710</v>
+        <v>57465</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520036</v>
+        <v>520030</v>
       </c>
       <c r="R3" t="n">
-        <v>6967788</v>
+        <v>6967798</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -852,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +896,7 @@
         <v>121483107</v>
       </c>
       <c r="B4" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1001,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121478101</v>
+        <v>121479593</v>
       </c>
       <c r="B5" t="n">
-        <v>57462</v>
+        <v>79688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,45 +1017,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520030</v>
+        <v>520021</v>
       </c>
       <c r="R5" t="n">
-        <v>6967798</v>
+        <v>6967787</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121479593</v>
+        <v>121479450</v>
       </c>
       <c r="B6" t="n">
-        <v>79685</v>
+        <v>90713</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,21 +1133,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520021</v>
+        <v>520036</v>
       </c>
       <c r="R6" t="n">
-        <v>6967787</v>
+        <v>6967788</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 16252-2024 artfynd.xlsx
+++ b/artfynd/A 16252-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121478101</v>
+        <v>121479450</v>
       </c>
       <c r="B3" t="n">
-        <v>57465</v>
+        <v>90713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520030</v>
+        <v>520036</v>
       </c>
       <c r="R3" t="n">
-        <v>6967798</v>
+        <v>6967788</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -856,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121483107</v>
+        <v>121478101</v>
       </c>
       <c r="B4" t="n">
-        <v>90713</v>
+        <v>57465</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,41 +901,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520123</v>
+        <v>520030</v>
       </c>
       <c r="R4" t="n">
-        <v>6967781</v>
+        <v>6967798</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1117,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121479450</v>
+        <v>121483107</v>
       </c>
       <c r="B6" t="n">
         <v>90713</v>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520036</v>
+        <v>520123</v>
       </c>
       <c r="R6" t="n">
-        <v>6967788</v>
+        <v>6967781</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 16252-2024 artfynd.xlsx
+++ b/artfynd/A 16252-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121479450</v>
+        <v>121478101</v>
       </c>
       <c r="B3" t="n">
-        <v>90713</v>
+        <v>57466</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520036</v>
+        <v>520030</v>
       </c>
       <c r="R3" t="n">
-        <v>6967788</v>
+        <v>6967798</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -852,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121478101</v>
+        <v>121483107</v>
       </c>
       <c r="B4" t="n">
-        <v>57465</v>
+        <v>90719</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,45 +905,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520030</v>
+        <v>520123</v>
       </c>
       <c r="R4" t="n">
-        <v>6967798</v>
+        <v>6967781</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121479593</v>
+        <v>121479450</v>
       </c>
       <c r="B5" t="n">
-        <v>79688</v>
+        <v>90719</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520021</v>
+        <v>520036</v>
       </c>
       <c r="R5" t="n">
-        <v>6967787</v>
+        <v>6967788</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121483107</v>
+        <v>121479593</v>
       </c>
       <c r="B6" t="n">
-        <v>90713</v>
+        <v>79689</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,21 +1133,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520123</v>
+        <v>520021</v>
       </c>
       <c r="R6" t="n">
-        <v>6967781</v>
+        <v>6967787</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 16252-2024 artfynd.xlsx
+++ b/artfynd/A 16252-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121478101</v>
+        <v>121479450</v>
       </c>
       <c r="B3" t="n">
-        <v>57466</v>
+        <v>90720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520030</v>
+        <v>520036</v>
       </c>
       <c r="R3" t="n">
-        <v>6967798</v>
+        <v>6967788</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -856,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121483107</v>
+        <v>121479593</v>
       </c>
       <c r="B4" t="n">
-        <v>90719</v>
+        <v>79690</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520123</v>
+        <v>520021</v>
       </c>
       <c r="R4" t="n">
-        <v>6967781</v>
+        <v>6967787</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121479450</v>
+        <v>121483107</v>
       </c>
       <c r="B5" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,13 +1041,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520036</v>
+        <v>520123</v>
       </c>
       <c r="R5" t="n">
-        <v>6967788</v>
+        <v>6967781</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121479593</v>
+        <v>121478101</v>
       </c>
       <c r="B6" t="n">
-        <v>79689</v>
+        <v>57467</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,41 +1125,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520021</v>
+        <v>520030</v>
       </c>
       <c r="R6" t="n">
-        <v>6967787</v>
+        <v>6967798</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 16252-2024 artfynd.xlsx
+++ b/artfynd/A 16252-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121479450</v>
+        <v>121483107</v>
       </c>
       <c r="B3" t="n">
         <v>90720</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520036</v>
+        <v>520123</v>
       </c>
       <c r="R3" t="n">
-        <v>6967788</v>
+        <v>6967781</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121479593</v>
+        <v>121479450</v>
       </c>
       <c r="B4" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520021</v>
+        <v>520036</v>
       </c>
       <c r="R4" t="n">
-        <v>6967787</v>
+        <v>6967788</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121483107</v>
+        <v>121479593</v>
       </c>
       <c r="B5" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520123</v>
+        <v>520021</v>
       </c>
       <c r="R5" t="n">
-        <v>6967781</v>
+        <v>6967787</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 16252-2024 artfynd.xlsx
+++ b/artfynd/A 16252-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121483107</v>
+        <v>121478101</v>
       </c>
       <c r="B3" t="n">
-        <v>90720</v>
+        <v>57467</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520123</v>
+        <v>520030</v>
       </c>
       <c r="R3" t="n">
-        <v>6967781</v>
+        <v>6967798</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1001,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121479593</v>
+        <v>121483107</v>
       </c>
       <c r="B5" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520021</v>
+        <v>520123</v>
       </c>
       <c r="R5" t="n">
-        <v>6967787</v>
+        <v>6967781</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121478101</v>
+        <v>121479593</v>
       </c>
       <c r="B6" t="n">
-        <v>57467</v>
+        <v>79690</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,45 +1129,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520030</v>
+        <v>520021</v>
       </c>
       <c r="R6" t="n">
-        <v>6967798</v>
+        <v>6967787</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 16252-2024 artfynd.xlsx
+++ b/artfynd/A 16252-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121478101</v>
+        <v>121483107</v>
       </c>
       <c r="B3" t="n">
-        <v>57467</v>
+        <v>90728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,45 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520030</v>
+        <v>520123</v>
       </c>
       <c r="R3" t="n">
-        <v>6967798</v>
+        <v>6967781</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121479450</v>
+        <v>121479593</v>
       </c>
       <c r="B4" t="n">
-        <v>90720</v>
+        <v>79697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520036</v>
+        <v>520021</v>
       </c>
       <c r="R4" t="n">
-        <v>6967788</v>
+        <v>6967787</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121483107</v>
+        <v>121479450</v>
       </c>
       <c r="B5" t="n">
-        <v>90720</v>
+        <v>90728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,13 +1041,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520123</v>
+        <v>520036</v>
       </c>
       <c r="R5" t="n">
-        <v>6967781</v>
+        <v>6967788</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121479593</v>
+        <v>121478101</v>
       </c>
       <c r="B6" t="n">
-        <v>79690</v>
+        <v>57468</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,41 +1125,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520021</v>
+        <v>520030</v>
       </c>
       <c r="R6" t="n">
-        <v>6967787</v>
+        <v>6967798</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 16252-2024 artfynd.xlsx
+++ b/artfynd/A 16252-2024 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121479450</v>
+        <v>121483107</v>
       </c>
       <c r="B4" t="n">
         <v>90728</v>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520036</v>
+        <v>520123</v>
       </c>
       <c r="R4" t="n">
-        <v>6967788</v>
+        <v>6967781</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121483107</v>
+        <v>121478101</v>
       </c>
       <c r="B5" t="n">
-        <v>90728</v>
+        <v>57468</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,41 +1013,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520123</v>
+        <v>520030</v>
       </c>
       <c r="R5" t="n">
-        <v>6967781</v>
+        <v>6967798</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121478101</v>
+        <v>121479450</v>
       </c>
       <c r="B6" t="n">
-        <v>57468</v>
+        <v>90728</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,42 +1129,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520030</v>
+        <v>520036</v>
       </c>
       <c r="R6" t="n">
-        <v>6967798</v>
+        <v>6967788</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 16252-2024 artfynd.xlsx
+++ b/artfynd/A 16252-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121479593</v>
+        <v>121483107</v>
       </c>
       <c r="B3" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520021</v>
+        <v>520123</v>
       </c>
       <c r="R3" t="n">
-        <v>6967787</v>
+        <v>6967781</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121483107</v>
+        <v>121479450</v>
       </c>
       <c r="B4" t="n">
         <v>90728</v>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520123</v>
+        <v>520036</v>
       </c>
       <c r="R4" t="n">
-        <v>6967781</v>
+        <v>6967788</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121479450</v>
+        <v>121479593</v>
       </c>
       <c r="B6" t="n">
-        <v>90728</v>
+        <v>79697</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,21 +1133,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520036</v>
+        <v>520021</v>
       </c>
       <c r="R6" t="n">
-        <v>6967788</v>
+        <v>6967787</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
